--- a/pre-week-3/Ex4B_more_GTrends.xlsx
+++ b/pre-week-3/Ex4B_more_GTrends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dagmawimulugeta\Documents\Data-analytics-2026\pre-week-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BC81F15-E476-4D2C-A109-52D69E8A3459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AAC52E-8077-4441-BBC9-5E75DE7320A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
   <si>
     <t>RegionID</t>
   </si>
@@ -655,114 +655,124 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B699002-ED13-4E11-9B5F-1512CFC93C11}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
         <v>0.85</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.9</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.82</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.8</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.78</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.77</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.76</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.79</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.74</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
         <v>0.78</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.72</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.7</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.75</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.68</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.65</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.66</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.69</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.64</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.63</v>
       </c>
     </row>

--- a/pre-week-3/Ex4B_more_GTrends.xlsx
+++ b/pre-week-3/Ex4B_more_GTrends.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dagmawimulugeta\Documents\Data-analytics-2026\pre-week-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AAC52E-8077-4441-BBC9-5E75DE7320A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578044A9-A935-4595-9656-062090A7F0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
